--- a/output/tables/Human_AI_vs_Priority_Results.xlsx
+++ b/output/tables/Human_AI_vs_Priority_Results.xlsx
@@ -54,7 +54,7 @@
     <t>0.11</t>
   </si>
   <si>
-    <t>Sleep</t>
+    <t>Sleep disruption</t>
   </si>
   <si>
     <t>0.06 (-0.01, 0.13)</t>
